--- a/backlog.xlsx
+++ b/backlog.xlsx
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ц.Номинзаяа</t>
+          <t>Ц.Номунзаяа</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ц.Номинзаяа</t>
+          <t>Ц.Номунзаяа</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ц.Номинзаяа</t>
+          <t>Ц.Номунзаяа</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ц.Номинзаяа</t>
+          <t>Ц.Номунзаяа</t>
         </is>
       </c>
       <c r="E10" t="n">

--- a/backlog.xlsx
+++ b/backlog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Product Backlog" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sprint 1 Backlog" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Kanban (дасгал)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Kanban (Sprint 1)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product Backlog" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint 1 Backlog" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kanban (дасгал)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kanban (Sprint 1)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Product Backlog'!$A$1:$I$16</definedName>
@@ -936,12 +936,12 @@
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Хасагдсан</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Must have</t>
+          <t>Won't have</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Хасагдсан</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Should have</t>
+          <t>Won't have</t>
         </is>
       </c>
     </row>

--- a/backlog.xlsx
+++ b/backlog.xlsx
@@ -691,12 +691,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>As a resident, I want to register my car with its plate number, so that it can be checked and approved.</t>
+          <t>As a resident, I want to register my car with its plate number, so that I can request a parking space for it right away.</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Оршин суугч машинаа улсын дугаараар бүртгүүлнэ.</t>
+          <t>Оршин суугч машинаа улсын дугаараар бүртгүүлмэгц машин идэвхтэй болно.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>As a manager, I want to approve or reject a registered car with a reason, so that only checked cars can rent a space.</t>
+          <t>As a manager, I want to cancel a car's registration with a reason when a complaint is confirmed, so that only residents' own cars wait for or hold a space.</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Менежер бүртгүүлсэн машиныг батална эсвэл шалтгаан бичиж татгалзана.</t>
+          <t>Гомдол үндэслэлтэй бол менежер машины бүртгэлийг шалтгаантай цуцалж, машины хүсэлт, түрээс цуцлагдана.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -953,12 +953,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>As a manager, I want to allocate a free space to the first request in the queue, so that the lease starts on the agreed date.</t>
+          <t>As a resident, I want to accept or decline a parking space offered to me within 48 hours, so that a free space never waits for a manager and goes to the next request if I do not need it.</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Менежер сул зогсоолыг дарааллын эхний хүсэлтэд олгоно.</t>
+          <t>Систем сул зогсоолыг дарааллын эхний хүсэлтэд санал болгож, оршин суугч 48 цагт баталгаажуулна. Татгалзвал эсвэл хариу өгөөгүй бол дараагийн хүсэлтэд шилжинэ.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1301,6 +1301,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -1451,12 +1452,12 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>As a resident, I want to register my car with its plate number, so that it can be checked and approved.</t>
+          <t>As a resident, I want to register my car with its plate number, so that I can request a parking space for it right away.</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Оршин суугч машинаа улсын дугаараар бүртгүүлнэ.</t>
+          <t>Оршин суугч машинаа улсын дугаараар бүртгүүлмэгц машин идэвхтэй болно.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1486,12 +1487,12 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>As a manager, I want to approve or reject a registered car with a reason, so that only checked cars can rent a space.</t>
+          <t>As a manager, I want to cancel a car's registration with a reason when a complaint is confirmed, so that only residents' own cars wait for or hold a space.</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Менежер бүртгүүлсэн машиныг батална эсвэл шалтгаан бичиж татгалзана.</t>
+          <t>Гомдол үндэслэлтэй бол менежер машины бүртгэлийг шалтгаантай цуцалж, машины хүсэлт, түрээс цуцлагдана.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2116,6 +2117,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
@@ -2296,7 +2298,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Машин батлах</t>
+          <t>Машины бүртгэл цуцлах</t>
         </is>
       </c>
       <c r="C8" t="n">
